--- a/documents/Web_Elements_IMAGES_REGISTER_StephyLiang.xlsx
+++ b/documents/Web_Elements_IMAGES_REGISTER_StephyLiang.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gogo/Downloads/web-project/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF54DAA9-CE09-9147-8BA8-60E1EBC53588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54884BDF-6C5F-FF41-9BF1-F14BB5713F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="98">
   <si>
     <t>File Name</t>
   </si>
@@ -85,9 +85,6 @@
     <t>MODIFICATIONS</t>
   </si>
   <si>
-    <t>&lt;image appears on which page&gt;</t>
-  </si>
-  <si>
     <t>https://pixabay.com/vectors/ai-generated-dog-puppy-cartoon-pet-7993565/</t>
   </si>
   <si>
@@ -314,15 +311,28 @@
   </si>
   <si>
     <t>resized,blur effect.Description: Understanding dietary requirements based on specific breed characteristics.</t>
+  </si>
+  <si>
+    <t>https://stephyliang-ux.github.io/web-project/</t>
+  </si>
+  <si>
+    <t>https://stephyliang-ux.github.io/web-project/html/gallery.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -564,77 +574,83 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1093,49 +1109,49 @@
     </row>
     <row r="4" spans="2:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="J4" s="14" t="s">
         <v>16</v>
       </c>
       <c r="K4" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="O4" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="P4" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>68</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>17</v>
@@ -1143,95 +1159,99 @@
     </row>
     <row r="5" spans="2:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="J5" s="14" t="s">
         <v>16</v>
       </c>
       <c r="K5" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="N5" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="L5" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="M5" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O5" s="9"/>
+      <c r="O5" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="P5" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:17" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="P6" s="9" t="s">
         <v>64</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="N6" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9" t="s">
-        <v>65</v>
       </c>
       <c r="Q6" s="1" t="s">
         <v>17</v>
@@ -1239,47 +1259,49 @@
     </row>
     <row r="7" spans="2:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="J7" s="14" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O7" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="P7" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="1" t="s">
         <v>17</v>
@@ -1287,47 +1309,49 @@
     </row>
     <row r="8" spans="2:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>22</v>
-      </c>
       <c r="E8" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H8" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="O8" s="9"/>
+        <v>70</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>96</v>
+      </c>
       <c r="P8" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q8" s="1" t="s">
         <v>17</v>
@@ -1335,45 +1359,47 @@
     </row>
     <row r="9" spans="2:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="12" t="s">
         <v>48</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>47</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>56</v>
-      </c>
       <c r="I9" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J9" s="14" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L9" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="9" t="s">
+      <c r="O9" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="P9" s="9" t="s">
         <v>59</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9" t="s">
-        <v>60</v>
       </c>
       <c r="Q9" s="1" t="s">
         <v>17</v>
@@ -1381,47 +1407,49 @@
     </row>
     <row r="10" spans="2:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>39</v>
-      </c>
       <c r="E10" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H10" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="J10" s="14" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O10" s="9"/>
+        <v>50</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>97</v>
+      </c>
       <c r="P10" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q10" s="1" t="s">
         <v>17</v>
@@ -1429,47 +1457,49 @@
     </row>
     <row r="11" spans="2:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>42</v>
-      </c>
       <c r="E11" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="J11" s="14" t="s">
         <v>16</v>
       </c>
       <c r="K11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="L11" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O11" s="9"/>
+      <c r="O11" s="9" t="s">
+        <v>97</v>
+      </c>
       <c r="P11" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="1" t="s">
         <v>17</v>
@@ -1477,47 +1507,49 @@
     </row>
     <row r="12" spans="2:17" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H12" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>37</v>
       </c>
       <c r="J12" s="14" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N12" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="O12" s="9"/>
+        <v>50</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>97</v>
+      </c>
       <c r="P12" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q12" s="1" t="s">
         <v>17</v>
@@ -1548,9 +1580,10 @@
     <hyperlink ref="C8" r:id="rId1" xr:uid="{E152E1B4-3762-D94B-A0E5-A40766742020}"/>
     <hyperlink ref="C4" r:id="rId2" xr:uid="{80ADB6E3-1734-B548-8381-8EBF67789E8E}"/>
     <hyperlink ref="C9" r:id="rId3" xr:uid="{EB6A33DF-13B1-A443-8B33-26C4CBB7E841}"/>
+    <hyperlink ref="O4" r:id="rId4" xr:uid="{74459143-0CAC-5046-92C8-3E0E1D9A1768}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
 
